--- a/jpcore-r4b/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-procedure.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -578,7 +578,7 @@
     <t>このプロシジャーが構成要素やステップとなるより大きな医療行為</t>
   </si>
   <si>
-    <t>【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
+    <t>【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
   </si>
   <si>
     <t>MedicationAdministrationリソースにはProcedureへのpartOf参照があるが、これは循環参照ではない。たとえば、麻酔MedicationAdministrationは外科的処置の一部である（MedicationAdministration.partOf = Procedure）。  
@@ -1589,7 +1589,7 @@
     <t>Kind of change to device</t>
   </si>
   <si>
-    <t>Procedure中にデバイスに起こった変化の種類。【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
+    <t>Procedure中にデバイスに起こった変化の種類。【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceAction_VS</t>
@@ -1608,7 +1608,7 @@
     <t>Device that was changed</t>
   </si>
   <si>
-    <t>Procedure中に操作（変更）されたデバイス。【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
+    <t>Procedure中に操作（変更）されたデバイス。【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
   </si>
   <si>
     <t>.participation[typeCode=DEV].role[classCode=SDLOC]</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3389" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3390" uniqueCount="524">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -367,7 +367,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -506,7 +506,7 @@
     <t>Procedure.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Measure|OperationDefinition|Questionnaire)
+    <t xml:space="preserve">canonical(PlanDefinition|4.3.0|ActivityDefinition|4.3.0|Measure|4.3.0|OperationDefinition|4.3.0|Questionnaire|4.3.0)
 </t>
   </si>
   <si>
@@ -544,7 +544,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.3.0|ServiceRequest|4.3.0)
 </t>
   </si>
   <si>
@@ -578,7 +578,7 @@
     <t>このプロシジャーが構成要素やステップとなるより大きな医療行為</t>
   </si>
   <si>
-    <t>【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
+    <t>【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
   </si>
   <si>
     <t>MedicationAdministrationリソースにはProcedureへのpartOf参照があるが、これは循環参照ではない。たとえば、麻酔MedicationAdministrationは外科的処置の一部である（MedicationAdministration.partOf = Procedure）。  
@@ -646,7 +646,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureNotPerformedReason_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureNotPerformedReason_VS|2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -812,7 +812,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/mhlw/CodeSystem/masterS-medicalProcedure</t>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ProcedureCodesMedical_CS</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1024,7 +1024,7 @@
     <t>Procedure.code.coding:nurse.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200119.4.701</t>
+    <t>http://medis.or.jp/CodeSystem/master-nursingAction-16digits</t>
   </si>
   <si>
     <t>Procedure.code.coding:nurse.version</t>
@@ -1048,7 +1048,7 @@
     <t>WHO ICHI (International Classification of Health Interventions) ValueSet</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesICHI_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesICHI_VS|2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Procedure.code.coding:ichi.id</t>
@@ -1138,13 +1138,13 @@
 </t>
   </si>
   <si>
-    <t>このプロシジャーの記録が作成された受療の状況</t>
-  </si>
-  <si>
-    <t>プロシジャーが作成または実行された受療の状況、またはこの記録の作成が緊密に関連している受療の状況。</t>
-  </si>
-  <si>
-    <t>これは通常、イベントが発生した出会いの中で行われるが、活動によっては、出会いの公式な終了前または終了後に開始されても、出会いの文脈と結びついている場合がある。</t>
+    <t>このプロシジャーの記録が作成されたEncounterの状況</t>
+  </si>
+  <si>
+    <t>プロシジャーが作成または実行されたEncounterの状況、またはこの記録の作成が緊密に関連している受療の状況。</t>
+  </si>
+  <si>
+    <t>これは通常、イベントが発生したEncounterの中で行われるが、活動によっては、Encounterの公式な終了前または終了後に開始されても、Encounterの文脈と結びついている場合がある。</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1288,7 +1288,7 @@
     <t>Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedurePerformerRole_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedurePerformerRole_VS|2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1393,7 +1393,7 @@
 もしプロシージャの異なる理由を説明しているのであれば、Procedure.reasonCodeとProcedure.reasonReferenceの両方を使用できる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureReason_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureReason_VS|2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1440,7 +1440,10 @@
     <t>ユースケースでBodySiteリソースの属性が必要な場合（たとえば、個別に識別して追跡するため）、標準の拡張extension [procedure-targetbodystructure]（extension-procedure-targetbodystructure.html）を使用する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureBodySite_VS</t>
+    <t>SNOMED CT Body site concepts</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.3.0</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1461,7 +1464,7 @@
     <t>結果に叙述的記述トのみが含まれている場合は、CodeableConcept.textを使用してその情報を格納できる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureOutcome_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureOutcome_VS|2.0.0-dev-temp</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=OUT].target.text</t>
@@ -1499,7 +1502,7 @@
     <t>合併症が叙述的なテキストによってのみ表現されている場合は、CodeableConcept.textに格納できる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCondition_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCondition_VS|2.0.0-dev-temp</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=OUTC].target[classCode=OBS, code="complication", moodCode=EVN].value</t>
@@ -1530,7 +1533,7 @@
     <t>If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureFollowUp_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureFollowUp_VS|2.0.0-dev-temp</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=ACT, moodCode=INT].code</t>
@@ -1589,10 +1592,10 @@
     <t>Kind of change to device</t>
   </si>
   <si>
-    <t>Procedure中にデバイスに起こった変化の種類。【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceAction_VS</t>
+    <t>Procedure中にデバイスに起こった変化の種類。【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceAction_VS|2.0.0-dev-temp</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="procedure device action"].value=:procedure device action codes</t>
@@ -1601,14 +1604,14 @@
     <t>Procedure.focalDevice.manipulated</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.3.0)
 </t>
   </si>
   <si>
     <t>Device that was changed</t>
   </si>
   <si>
-    <t>Procedure中に操作（変更）されたデバイス。【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
+    <t>Procedure中に操作（変更）されたデバイス。【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
   </si>
   <si>
     <t>.participation[typeCode=DEV].role[classCode=SDLOC]</t>
@@ -1646,7 +1649,7 @@
     <t>Procedureの一部として使用されたコード化されたアイテムを識別する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceKind_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceKind_VS|2.0.0-dev-temp</t>
   </si>
   <si>
     <t>participation[typeCode=Dev].role[classCode=MANU]</t>
@@ -1956,17 +1959,17 @@
   <dimension ref="A1:AN93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.45703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.3984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.2890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="227.4375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1975,26 +1978,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="42.5234375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.18359375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="36.45703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.41015625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="142.56640625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="122.22265625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="90.15625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10976,9 +10979,11 @@
       <c r="X79" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Y79" s="2"/>
+      <c r="Y79" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -11014,21 +11019,21 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11054,13 +11059,13 @@
         <v>196</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11090,7 +11095,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11108,7 +11113,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11126,7 +11131,7 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -11137,10 +11142,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11163,16 +11168,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11222,7 +11227,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11240,7 +11245,7 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -11251,10 +11256,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11280,13 +11285,13 @@
         <v>196</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11316,7 +11321,7 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11334,7 +11339,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11352,7 +11357,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11363,10 +11368,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11389,19 +11394,19 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>382</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11450,7 +11455,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11468,7 +11473,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11479,10 +11484,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11508,10 +11513,10 @@
         <v>196</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11542,7 +11547,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -11560,7 +11565,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11578,7 +11583,7 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -11589,10 +11594,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11615,16 +11620,16 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11674,7 +11679,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11689,24 +11694,24 @@
         <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11732,10 +11737,10 @@
         <v>391</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11786,7 +11791,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11804,7 +11809,7 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
@@ -11815,10 +11820,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11927,10 +11932,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12041,10 +12046,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12157,10 +12162,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12186,10 +12191,10 @@
         <v>196</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12220,7 +12225,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -12238,7 +12243,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12256,7 +12261,7 @@
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12267,10 +12272,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12293,13 +12298,13 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12350,7 +12355,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>89</v>
@@ -12368,7 +12373,7 @@
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12379,10 +12384,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12405,19 +12410,19 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -12466,7 +12471,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12484,7 +12489,7 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12495,10 +12500,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12524,13 +12529,13 @@
         <v>196</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12560,7 +12565,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -12578,7 +12583,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12596,7 +12601,7 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-procedure.xlsx
@@ -578,7 +578,7 @@
     <t>このプロシジャーが構成要素やステップとなるより大きな医療行為</t>
   </si>
   <si>
-    <t>【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
+    <t>【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
   </si>
   <si>
     <t>MedicationAdministrationリソースにはProcedureへのpartOf参照があるが、これは循環参照ではない。たとえば、麻酔MedicationAdministrationは外科的処置の一部である（MedicationAdministration.partOf = Procedure）。  
@@ -1592,7 +1592,7 @@
     <t>Kind of change to device</t>
   </si>
   <si>
-    <t>Procedure中にデバイスに起こった変化の種類。【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
+    <t>Procedure中にデバイスに起こった変化の種類。【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceAction_VS|2.0.0-dev-temp</t>
@@ -1611,7 +1611,7 @@
     <t>Device that was changed</t>
   </si>
   <si>
-    <t>Procedure中に操作（変更）されたデバイス。【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
+    <t>Procedure中に操作（変更）されたデバイス。【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
   </si>
   <si>
     <t>.participation[typeCode=DEV].role[classCode=SDLOC]</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-procedure.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -646,7 +646,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureNotPerformedReason_VS|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureNotPerformedReason_VS|2.0.0-dev</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -1048,7 +1048,7 @@
     <t>WHO ICHI (International Classification of Health Interventions) ValueSet</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesICHI_VS|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesICHI_VS|2.0.0-dev</t>
   </si>
   <si>
     <t>Procedure.code.coding:ichi.id</t>
@@ -1288,7 +1288,7 @@
     <t>Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedurePerformerRole_VS|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedurePerformerRole_VS|2.0.0-dev</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1393,7 +1393,7 @@
 もしプロシージャの異なる理由を説明しているのであれば、Procedure.reasonCodeとProcedure.reasonReferenceの両方を使用できる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureReason_VS|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureReason_VS|2.0.0-dev</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1464,7 +1464,7 @@
     <t>結果に叙述的記述トのみが含まれている場合は、CodeableConcept.textを使用してその情報を格納できる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureOutcome_VS|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureOutcome_VS|2.0.0-dev</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=OUT].target.text</t>
@@ -1502,7 +1502,7 @@
     <t>合併症が叙述的なテキストによってのみ表現されている場合は、CodeableConcept.textに格納できる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCondition_VS|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCondition_VS|2.0.0-dev</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=OUTC].target[classCode=OBS, code="complication", moodCode=EVN].value</t>
@@ -1533,7 +1533,7 @@
     <t>If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureFollowUp_VS|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureFollowUp_VS|2.0.0-dev</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=ACT, moodCode=INT].code</t>
@@ -1595,7 +1595,7 @@
     <t>Procedure中にデバイスに起こった変化の種類。【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceAction_VS|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceAction_VS|2.0.0-dev</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="procedure device action"].value=:procedure device action codes</t>
@@ -1649,7 +1649,7 @@
     <t>Procedureの一部として使用されたコード化されたアイテムを識別する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceKind_VS|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceKind_VS|2.0.0-dev</t>
   </si>
   <si>
     <t>participation[typeCode=Dev].role[classCode=MANU]</t>
@@ -1984,7 +1984,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="36.45703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.41015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.73046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4b/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-procedure.xlsx
@@ -268,8 +268,8 @@
     <t>患者に対して、または患者のために実行されているか実行されたアクション。これは、手術のような身体的介入、または長期サービス、カウンセリング、催眠療法のような低侵襲性である可能性がある。</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -297,10 +297,10 @@
     <t>Logical id of this artifact</t>
   </si>
   <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -313,16 +313,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -333,13 +333,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -352,19 +352,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -387,10 +387,10 @@
     <t>このリソースを人間が解釈するためのテキスト要約</t>
   </si>
   <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -413,16 +413,16 @@
     <t>Contained, inline Resources</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -440,33 +440,34 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Procedure.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -479,7 +480,7 @@
 </t>
   </si>
   <si>
-    <t>External Identifiers for this procedure</t>
+    <t>このプロシジャー（処置等）の外部identifier / External Identifiers for this procedure</t>
   </si>
   <si>
     <t>これは、ビジネスプロセスによって定義され、リソース自体への直接のURL参照が適切でない場合に参照するために使用される、このProcedureに関連する識別子を記録する。</t>
@@ -488,7 +489,7 @@
     <t>これはビジネス識別子であり、リソース識別子ではない（議論参照）。識別子は1つのリソースインスタンスにのみ表示されることがベストだが、ビジネス上の慣習により、同じ識別子を持つ複数のリソースインスタンスが存在することがあるかもしれない。例えば、複数のPatientとPersonリソースインスタンスが同じ社会保険番号を共有しているかもしれない。</t>
   </si>
   <si>
-    <t>Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
+    <t>さまざまな参加システムで知られており、サーバー全体で一貫性のある方法で知られているプロシジャー（処置等）を識別できます。 / Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -510,7 +511,7 @@
 </t>
   </si>
   <si>
-    <t>Instantiates FHIR protocol or definition</t>
+    <t>FHIRプロトコルまたは定義をインスタンス化します / Instantiates FHIR protocol or definition</t>
   </si>
   <si>
     <t>本Procedureの全部または一部を遵守するFHIR定義のプロトコル、ガイドライン、オーダセット、その他の定義を指すURL。</t>
@@ -525,13 +526,13 @@
     <t>Procedure.instantiatesUri</t>
   </si>
   <si>
-    <t>Instantiates external protocol or definition</t>
+    <t>外部プロトコルまたは定義をインスタンス化します / Instantiates external protocol or definition</t>
   </si>
   <si>
     <t>本Procedure全体または一部を遵守する、外部で管理されているプロトコル、ガイドライン、オーダセット、またはその他の定義を指すURL。</t>
   </si>
   <si>
-    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+    <t>これは、HTMLページ、PDFなどである可能性があるか、単に解決できないURIidentifierである可能性があります。 / This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
   </si>
   <si>
     <t>Event.instantiatesUri</t>
@@ -595,7 +596,7 @@
     <t>Procedure.status</t>
   </si>
   <si>
-    <t>preparation | in-progress | not-done | on-hold | stopped | completed | entered-in-error | unknown</t>
+    <t>準備中 | 進行中 | 未完了 | 保留 | 停止 | 完了 | エラー入力 | 不明 / preparation | in-progress | not-done | on-hold | stopped | completed | entered-in-error | unknown</t>
   </si>
   <si>
     <t>プロシージャの状態を指定するコードである。一般的には、進行中または完了した状態になる。【JP Core仕様】http://hl7.org/fhir/us/core/STU3.1/StructureDefinition-us-core-procedure.htmlを参照</t>
@@ -608,7 +609,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>A code specifying the state of the procedure.</t>
+    <t>プロシジャー（処置等）の状態を指定するコード。 / A code specifying the state of the procedure.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/event-status|4.3.0</t>
@@ -661,7 +662,7 @@
     <t>このプロシジャーの分類カテゴリ</t>
   </si>
   <si>
-    <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
+    <t>検索、並べ替え、表示のプロシジャー（処置等）を分類するコード（「外科的処置」など）。 / A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCategory_VS</t>
@@ -689,7 +690,7 @@
     <t>すべての用語の使用がこの一般的なパターンに当てはまるわけではない。場合によっては、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係や事前・事後の調整を管理するための独自の構造を提供すべきである。</t>
   </si>
   <si>
-    <t>0..1 to account for primarily narrative only resources.</t>
+    <t>0..1主に叙述(Narative)のみのリソースを説明する。 / 0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesMedical_VS</t>
@@ -710,10 +711,10 @@
     <t>Procedure.code.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -725,7 +726,7 @@
     <t>Procedure.code.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -748,16 +749,16 @@
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -800,16 +801,16 @@
     <t>Procedure.code.coding.system</t>
   </si>
   <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ProcedureCodesMedical_CS</t>
@@ -834,13 +835,13 @@
 </t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
   </si>
   <si>
     <t>Coding.version</t>
@@ -858,13 +859,13 @@
     <t>Procedure.code.coding.code</t>
   </si>
   <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -882,13 +883,13 @@
     <t>Procedure.code.coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
     <t>Coding.display</t>
@@ -910,16 +911,16 @@
 </t>
   </si>
   <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
   </si>
   <si>
     <t>Coding.userSelected</t>
@@ -1078,16 +1079,16 @@
     <t>Procedure.code.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -1239,7 +1240,7 @@
     <t>医療機器ではなく「生身の人間」に限定。</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1262,10 +1263,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1285,7 +1287,7 @@
  【JP Core仕様】当面利用しない。</t>
   </si>
   <si>
-    <t>Allows disambiguation of the types of involvement of different performers.</t>
+    <t>さまざまなパフォーマーの関与の種類の曖昧性を乱すことができます。 / Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedurePerformerRole_VS|2.0.0-dev</t>
@@ -1316,7 +1318,7 @@
     <t>参照は、実際のFHIRリソースへの参照であり、解決可能でなければならない（アクセス制御、一時的な利用不可などを可能にする）。解決には、URLからの検索、またはリソースタイプによって適用可能な場合は、絶対参照を正規のURLとして扱い、ローカルレジストリ/リポジトリで検索することができる。</t>
   </si>
   <si>
-    <t>A reference to Device supports use cases, such as pacemakers.</t>
+    <t>デバイスへの参照は、ペースメーカーなどのユースケースをサポートします。 / A reference to Device supports use cases, such as pacemakers.</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1347,7 +1349,7 @@
     <t>参照は、実際のFHIRリソースへの参照であり、解決可能でなければならない（アクセス制御、一時的な利用不能などを可能にする）。解決には、URLからの検索によるものと、リソースタイプによって該当する場合は、絶対参照を正規のURLとして扱い、ローカルレジストリ/リポジトリで検索するものがある。</t>
   </si>
   <si>
-    <t>Practitioners and Devices can be associated with multiple organizations.  This element indicates which organization they were acting on behalf of when performing the action.</t>
+    <t>開業医とデバイスは、複数の組織に関連付けられています。この要素は、アクションを実行する際にどの組織が行動していたかを示します。 / Practitioners and Devices can be associated with multiple organizations.  This element indicates which organization they were acting on behalf of when performing the action.</t>
   </si>
   <si>
     <t>.scoper</t>
@@ -1367,7 +1369,7 @@
 例:自宅での出生、レストランで気管切開など。</t>
   </si>
   <si>
-    <t>Ties a procedure to where the records are likely kept.</t>
+    <t>記録が保持される可能性が高い場所にプロシジャー（処置等）を結びます。 / Ties a procedure to where the records are likely kept.</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role[classCode=SDLOC]</t>
@@ -1440,7 +1442,7 @@
     <t>ユースケースでBodySiteリソースの属性が必要な場合（たとえば、個別に識別して追跡するため）、標準の拡張extension [procedure-targetbodystructure]（extension-procedure-targetbodystructure.html）を使用する。</t>
   </si>
   <si>
-    <t>SNOMED CT Body site concepts</t>
+    <t>SNOMED CT身体部位概念 / SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site|4.3.0</t>
@@ -1530,7 +1532,7 @@
     <t>今後の処置が特別なフォローアップを必要とする場合（例：抜糸）、フォローアップはシンプルなnote として表現してもよいが、より複雑になる可能性もあり、その場合はケアプランリソースを使用することができる。</t>
   </si>
   <si>
-    <t>If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
+    <t>プロシジャー（処置等）で特定のフォローアップが必要な場合 - 例えば縫合の除去。フォローアップは、単純なメモとして表されるか、潜在的により複雑になる可能性があります。その場合、カレプランリソースを使用できます。 / If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureFollowUp_VS|2.0.0-dev</t>
@@ -1589,7 +1591,7 @@
     <t>Procedure.focalDevice.action</t>
   </si>
   <si>
-    <t>Kind of change to device</t>
+    <t>デバイスへの変更の種類 / Kind of change to device</t>
   </si>
   <si>
     <t>Procedure中にデバイスに起こった変化の種類。【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
@@ -1608,7 +1610,7 @@
 </t>
   </si>
   <si>
-    <t>Device that was changed</t>
+    <t>変更されたデバイス / Device that was changed</t>
   </si>
   <si>
     <t>Procedure中に操作（変更）されたデバイス。【JP Core仕様】https://www.hl7.org/fhir/R4B/procedure.htmlを参照</t>
@@ -1633,7 +1635,7 @@
     <t>実際に埋め込まれた、または取り外されたデバイスについては、Procedure.deviceを使用すること。</t>
   </si>
   <si>
-    <t>Used for tracking contamination, etc.</t>
+    <t>汚染などの追跡に使用されます。 / Used for tracking contamination, etc.</t>
   </si>
   <si>
     <t>.participation[typeCode=DEV].role[classCode=MANU] or
@@ -1983,7 +1985,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="36.45703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="59.6796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="64.73046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
